--- a/02_DIA_inicio_2026_analisis_assets/rbd_9599_liceo-purkuyen_nt1_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9599_liceo-purkuyen_nt1_rubricas.xlsx
@@ -1920,13 +1920,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FF098E1-A568-4B7F-9F2D-8596856210AA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E62C550B-F4D5-415C-90FD-06B71F1905A3}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E43A76D6-A709-4651-853A-216329FA58D7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{579BEE33-958C-47FA-B09D-2C9EDF5467BA}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C63B2B4C-29E6-4F15-9BE6-BB3C17384D1A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD87FDD7-09DF-47C3-9EAA-7F29E6B233EA}"/>
 </file>